--- a/utils/monday_sprint_sprint_2023-25.xlsx
+++ b/utils/monday_sprint_sprint_2023-25.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="135">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,27 +63,45 @@
     <t>5623785026</t>
   </si>
   <si>
-    <t>Sprint 2023-25</t>
+    <t>Setor não informado</t>
   </si>
   <si>
     <t>Indefinido</t>
   </si>
   <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Atividades Diversas</t>
+  </si>
+  <si>
+    <t>Não definida</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>04/12/2023</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Atividades Diversas</t>
-  </si>
-  <si>
-    <t>Não definida</t>
-  </si>
-  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>Não</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
     <t>5623785103</t>
   </si>
   <si>
@@ -99,6 +120,9 @@
     <t>Média</t>
   </si>
   <si>
+    <t>01/12/2023</t>
+  </si>
+  <si>
     <t>23507</t>
   </si>
   <si>
@@ -294,6 +318,9 @@
     <t>Sistema Novo de Revisão de Documentos - Sprint 3/4 - Desenvolvimento</t>
   </si>
   <si>
+    <t>11/12/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -345,7 +372,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -363,10 +390,10 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -807,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -817,13 +844,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,1721 +895,1841 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="K4" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="D39" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>17</v>
+        <v>102</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -2596,23 +2745,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2620,16 +2769,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2640,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>10.62</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2648,12 +2797,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K22">
         <v>39</v>
@@ -2661,7 +2810,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2669,7 +2818,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2700,12 +2849,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B2">
         <v>39</v>
@@ -2719,7 +2868,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>10.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2729,60 +2878,60 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E10">
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N10">
         <v>39</v>
       </c>
       <c r="P10" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q10">
         <v>37</v>
@@ -2790,31 +2939,31 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>116</v>
+        <v>26</v>
       </c>
       <c r="K11">
         <v>39</v>
       </c>
       <c r="M11" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="Q11">
         <v>2</v>
@@ -2822,19 +2971,25 @@
     </row>
     <row r="12" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="H12">
         <v>35</v>
       </c>
+      <c r="J12" t="s">
+        <v>126</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2842,13 +2997,13 @@
     </row>
     <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2856,13 +3011,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2870,7 +3025,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2878,7 +3033,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2886,7 +3041,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2894,7 +3049,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -2905,7 +3060,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2913,142 +3068,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2023-25.xlsx
+++ b/utils/monday_sprint_sprint_2023-25.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="151">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>04/12/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>25/12/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -108,7 +108,7 @@
     <t>5623785218</t>
   </si>
   <si>
-    <t>23510</t>
+    <t>5608566169</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -123,43 +123,55 @@
     <t>01/12/2023</t>
   </si>
   <si>
-    <t>23507</t>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>5608580553</t>
   </si>
   <si>
     <t>Relatório do sistema de corridas o forno 10</t>
   </si>
   <si>
-    <t>23505</t>
+    <t>5608590488</t>
   </si>
   <si>
     <t>Melhoria na Carteira de Orçamentos Ativos</t>
   </si>
   <si>
-    <t>23491</t>
+    <t>14/12/2023</t>
+  </si>
+  <si>
+    <t>5608602547</t>
   </si>
   <si>
     <t>ERRO 22319 - Obrigatório OTF para requisições de materiais</t>
   </si>
   <si>
-    <t>23487</t>
+    <t>12/12/2023</t>
+  </si>
+  <si>
+    <t>5608618869</t>
   </si>
   <si>
     <t>LOG DE EVENTOS CPP</t>
   </si>
   <si>
-    <t>23479</t>
+    <t>5608663802</t>
   </si>
   <si>
     <t>[MELHORIA SUPRIMENTOS] NOVOS STATUS DO FORNECEDOR</t>
   </si>
   <si>
-    <t>23461</t>
+    <t>10/12/2023</t>
+  </si>
+  <si>
+    <t>5608835562</t>
   </si>
   <si>
     <t>Projeto WMS - Logística interna</t>
   </si>
   <si>
-    <t>23414</t>
+    <t>5608869132</t>
   </si>
   <si>
     <t>[MELHORIA / IMPLANTAÇÃO NIMBI] Preenchimento da família no cadastro do material (recategorização)</t>
@@ -168,121 +180,139 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>23459</t>
+    <t>05/12/2023</t>
+  </si>
+  <si>
+    <t>5608901833</t>
   </si>
   <si>
     <t>Aprovação de orçamento_ Estouro de orçamento</t>
   </si>
   <si>
-    <t>23455</t>
+    <t>13/12/2023</t>
+  </si>
+  <si>
+    <t>5608923929</t>
   </si>
   <si>
     <t>Consulta de SIC's de investimentos</t>
   </si>
   <si>
-    <t>23441</t>
+    <t>07/12/2023</t>
+  </si>
+  <si>
+    <t>5608975585</t>
   </si>
   <si>
     <t>WMS - Log interna</t>
   </si>
   <si>
-    <t>23440</t>
+    <t>5610120818</t>
   </si>
   <si>
     <t>WMS - Log interna II</t>
   </si>
   <si>
-    <t>23437</t>
+    <t>5610135344</t>
   </si>
   <si>
     <t>MIGRAÇÃO DE SEQUÊNCIAS DE PRODUTIVO</t>
   </si>
   <si>
-    <t>23431</t>
+    <t>16/12/2023</t>
+  </si>
+  <si>
+    <t>5610149817</t>
   </si>
   <si>
     <t>Tela para visualização do log de eventos</t>
   </si>
   <si>
-    <t>23427</t>
+    <t>5610190369</t>
   </si>
   <si>
     <t>Ajuste Observações da Invoice</t>
   </si>
   <si>
-    <t>23419</t>
+    <t>5610217621</t>
   </si>
   <si>
     <t>[MELHORIA / IMPLANTAÇÃO NIMBI] - Saneamento nas unidades de medida dos cadastros dos materiais</t>
   </si>
   <si>
-    <t>23413</t>
+    <t>5610233975</t>
   </si>
   <si>
     <t>[MELHORIA / IMPLANTAÇÃO NIMBI] Inativação prazos de pagamento</t>
   </si>
   <si>
-    <t>23397</t>
+    <t>5610401394</t>
   </si>
   <si>
     <t>Problema no vencimento</t>
   </si>
   <si>
-    <t>23395</t>
+    <t>5610422155</t>
   </si>
   <si>
     <t>Consultar informação de estorno na tela do fluxo de produção</t>
   </si>
   <si>
-    <t>23355</t>
+    <t>5610490167</t>
   </si>
   <si>
     <t>Apontamento de Inspeção</t>
   </si>
   <si>
-    <t>23351</t>
+    <t>5610497160</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Integrator - Documento Contábil</t>
   </si>
   <si>
-    <t>23350</t>
+    <t>5610728942</t>
   </si>
   <si>
     <t>Altona || Sistema ERP || Integrator - Data CTE X Data NFe</t>
   </si>
   <si>
-    <t>23349</t>
+    <t>06/12/2023</t>
+  </si>
+  <si>
+    <t>5610735193</t>
   </si>
   <si>
     <t>Acesso ao Banco de Dados - Estorno</t>
   </si>
   <si>
-    <t>23261</t>
+    <t>5610872208</t>
   </si>
   <si>
     <t>Movimentação 9996</t>
   </si>
   <si>
-    <t>23125</t>
+    <t>5610910698</t>
   </si>
   <si>
     <t>Registro de moldagem</t>
   </si>
   <si>
-    <t>23548</t>
+    <t>11/12/2023</t>
+  </si>
+  <si>
+    <t>5611056378</t>
   </si>
   <si>
     <t>Revisão do sistema de mov. peças para usinagem de terceiros</t>
   </si>
   <si>
-    <t>23514</t>
+    <t>5611081882</t>
   </si>
   <si>
     <t>Mudanças no sistema</t>
   </si>
   <si>
-    <t>23467</t>
+    <t>5608670369</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -291,39 +321,54 @@
     <t>PDI Eletrônico - Atividade I</t>
   </si>
   <si>
+    <t>5608683165</t>
+  </si>
+  <si>
     <t>PDI Eletrônico - Atividade II</t>
   </si>
   <si>
+    <t>5608688691</t>
+  </si>
+  <si>
     <t>PDI Eletrônico - Atividade III</t>
   </si>
   <si>
+    <t>5608726113</t>
+  </si>
+  <si>
     <t>PDI Eletrõnico - Atividade V</t>
   </si>
   <si>
+    <t>5608772552</t>
+  </si>
+  <si>
     <t>PDI Elerõnico - Atividade VI</t>
   </si>
   <si>
+    <t>5608787784</t>
+  </si>
+  <si>
     <t>PDI Eletrônico - Atividade VII</t>
   </si>
   <si>
-    <t>23410</t>
+    <t>5610393381</t>
   </si>
   <si>
     <t>[MELHORIA / IMPLATAÇÃO NIMBI] - Bloqueio Condição de pagamento</t>
   </si>
   <si>
-    <t>6090</t>
+    <t>5661535274</t>
   </si>
   <si>
     <t>Sistema Novo de Revisão de Documentos - Sprint 3/4 - Desenvolvimento</t>
   </si>
   <si>
-    <t>11/12/2023</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
+    <t>5661537900</t>
+  </si>
+  <si>
     <t>Sistema Novo de Revisão de Documentos - Sprint 3/4 - Testes</t>
   </si>
   <si>
@@ -333,7 +378,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-25</t>
+    <t>Dez/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -387,9 +432,6 @@
     <t>Muito Alta</t>
   </si>
   <si>
-    <t>Sim</t>
-  </si>
-  <si>
     <t>A fazer</t>
   </si>
   <si>
@@ -399,10 +441,16 @@
     <t>Impedimento</t>
   </si>
   <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
     <t>Baixa</t>
   </si>
   <si>
     <t>Fazendo</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -1072,13 +1120,13 @@
         <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1089,7 +1137,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1101,10 +1149,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>34</v>
@@ -1119,13 +1167,13 @@
         <v>35</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1136,7 +1184,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1148,10 +1196,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>34</v>
@@ -1166,13 +1214,13 @@
         <v>35</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1183,7 +1231,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1195,10 +1243,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>34</v>
@@ -1213,13 +1261,13 @@
         <v>35</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1230,7 +1278,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1242,10 +1290,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>34</v>
@@ -1260,13 +1308,13 @@
         <v>35</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1277,7 +1325,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1289,10 +1337,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>34</v>
@@ -1307,13 +1355,13 @@
         <v>35</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -1324,7 +1372,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1336,10 +1384,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>34</v>
@@ -1354,13 +1402,13 @@
         <v>35</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1371,7 +1419,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1383,13 +1431,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>21</v>
@@ -1401,13 +1449,13 @@
         <v>35</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>27</v>
@@ -1418,7 +1466,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1430,10 +1478,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>34</v>
@@ -1448,13 +1496,13 @@
         <v>35</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>27</v>
@@ -1465,7 +1513,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1477,10 +1525,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>34</v>
@@ -1495,13 +1543,13 @@
         <v>35</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>27</v>
@@ -1512,7 +1560,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1524,10 +1572,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>34</v>
@@ -1542,13 +1590,13 @@
         <v>35</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1559,7 +1607,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1571,10 +1619,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>34</v>
@@ -1589,13 +1637,13 @@
         <v>35</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>27</v>
@@ -1606,7 +1654,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1618,10 +1666,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>34</v>
@@ -1636,7 +1684,7 @@
         <v>35</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1653,7 +1701,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1665,10 +1713,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>34</v>
@@ -1683,13 +1731,13 @@
         <v>35</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>27</v>
@@ -1700,7 +1748,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1712,10 +1760,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>34</v>
@@ -1730,13 +1778,13 @@
         <v>35</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>27</v>
@@ -1747,7 +1795,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1759,10 +1807,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>34</v>
@@ -1777,13 +1825,13 @@
         <v>35</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>27</v>
@@ -1794,7 +1842,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1806,10 +1854,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>34</v>
@@ -1824,13 +1872,13 @@
         <v>35</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>27</v>
@@ -1841,7 +1889,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1853,10 +1901,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>34</v>
@@ -1871,13 +1919,13 @@
         <v>35</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>27</v>
@@ -1888,7 +1936,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1900,10 +1948,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>34</v>
@@ -1918,7 +1966,7 @@
         <v>35</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1935,7 +1983,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1947,10 +1995,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>34</v>
@@ -1965,7 +2013,7 @@
         <v>35</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1982,7 +2030,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1994,10 +2042,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>34</v>
@@ -2012,13 +2060,13 @@
         <v>35</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>27</v>
@@ -2029,7 +2077,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2041,10 +2089,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>34</v>
@@ -2059,13 +2107,13 @@
         <v>35</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
@@ -2076,7 +2124,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2088,10 +2136,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>34</v>
@@ -2106,13 +2154,13 @@
         <v>35</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>27</v>
@@ -2123,7 +2171,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2135,10 +2183,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>34</v>
@@ -2153,7 +2201,7 @@
         <v>35</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2170,7 +2218,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2182,10 +2230,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>34</v>
@@ -2200,13 +2248,13 @@
         <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
@@ -2217,7 +2265,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2229,10 +2277,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>34</v>
@@ -2247,13 +2295,13 @@
         <v>35</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>27</v>
@@ -2264,7 +2312,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2276,10 +2324,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>34</v>
@@ -2294,13 +2342,13 @@
         <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>27</v>
@@ -2311,22 +2359,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>34</v>
@@ -2341,13 +2389,13 @@
         <v>35</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>27</v>
@@ -2358,22 +2406,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>34</v>
@@ -2388,13 +2436,13 @@
         <v>35</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
@@ -2405,22 +2453,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>34</v>
@@ -2435,13 +2483,13 @@
         <v>35</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>27</v>
@@ -2452,22 +2500,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>34</v>
@@ -2482,13 +2530,13 @@
         <v>35</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>27</v>
@@ -2499,22 +2547,22 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>34</v>
@@ -2529,13 +2577,13 @@
         <v>35</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
@@ -2546,22 +2594,22 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>34</v>
@@ -2576,13 +2624,13 @@
         <v>35</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2593,7 +2641,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2605,10 +2653,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>34</v>
@@ -2623,13 +2671,13 @@
         <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>27</v>
@@ -2640,22 +2688,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>34</v>
@@ -2667,10 +2715,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2679,7 +2727,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -2687,22 +2735,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>34</v>
@@ -2714,10 +2762,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2726,7 +2774,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -2745,23 +2793,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2769,16 +2817,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2786,10 +2834,10 @@
         <v>39</v>
       </c>
       <c r="D5" s="5">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>10.62</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2797,7 +2845,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2810,7 +2858,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2818,7 +2866,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2836,7 +2884,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q30"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -2849,12 +2897,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B2">
         <v>39</v>
@@ -2862,13 +2910,13 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2878,25 +2926,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2913,16 +2961,16 @@
         <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>124</v>
+        <v>36</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -2934,18 +2982,18 @@
         <v>27</v>
       </c>
       <c r="Q10">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2954,22 +3002,22 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="M11" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="Q11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="4:14" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>17</v>
       </c>
@@ -2983,30 +3031,42 @@
         <v>35</v>
       </c>
       <c r="J12" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
+      <c r="P12" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="N13">
         <v>0</v>
+      </c>
+      <c r="P13" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -3017,7 +3077,7 @@
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3025,7 +3085,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3033,7 +3093,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3041,7 +3101,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3049,10 +3109,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -3060,7 +3120,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3074,7 +3134,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -3088,7 +3148,7 @@
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -3102,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -3110,100 +3170,86 @@
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="2">
-        <v>0</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
